--- a/artfynd/A 58641-2022 artfynd.xlsx
+++ b/artfynd/A 58641-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58641-2022 artfynd.xlsx
+++ b/artfynd/A 58641-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83456628</v>
+        <v>83449729</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463328.3155817588</v>
+        <v>463382</v>
       </c>
       <c r="R2" t="n">
-        <v>6245444.580056102</v>
+        <v>6245495</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>51DB2BA4-8E46-467C-97E1-9666713F47CD</t>
+          <t>D2A889AC-3284-4D56-8B10-470A486566C4</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,19 +752,9 @@
           <t>2006-10-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -798,6 +783,121 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>83456628</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>463328</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6245445</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>51DB2BA4-8E46-467C-97E1-9666713F47CD</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2006-10-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2006-10-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>inventerat av Naturskyddsföreningen i Skåne, Inge Stenberg, Anna Fohrman m fl</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Levenskog</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Levenskog</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
